--- a/dados/coletas/coleta_2026-10-16.xlsx
+++ b/dados/coletas/coleta_2026-10-16.xlsx
@@ -10,7 +10,7 @@
     <sheet name="coleta" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'coleta'!$A$1:$H$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'coleta'!$A$1:$I$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,17 +433,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,37 +455,42 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>loja</t>
+          <t>nome_loja</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>url_base</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nome_produto</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>categoria_produto</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>nome_produto</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>preco</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>url_oferta</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>titulo_anuncio</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>preco</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>preco_prazo</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>url_oferta</t>
         </is>
       </c>
     </row>
@@ -494,34 +500,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Processador AMD Ryzen 7 5700X</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Processador</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Processador AMD Ryzen 7 5700X</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Processador AMD Ryzen 7 5700X, 3.4GHz (4.6GHz Max Turbo), Cache 36MB, 8 Núcleos, 16 Threads, AM4, Sem Vídeo Integrado - 100-100000926WOF</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>1199.99</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/320797/processador-amd-ryzen-7-5700x-3-4ghz-4-6ghz-max-turbo-cache-36mb-8-nucleos-16-threads-am4-sem-video-integrado-100-100000926wof</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Processador AMD Ryzen 7 5700X, 3.4GHz (4.6GHz Max Turbo), Cache 36MB, 8 Núcleos, 16 Threads, AM4, Sem Vídeo Integrado - 100-100000926WOF</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>2245.81</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/320797/processador-amd-ryzen-7-5700x-3-4ghz-4-6ghz-max-turbo-cache-36mb-8-nucleos-16-threads-am4-sem-video-integrado-100-100000926wof</t>
-        </is>
       </c>
     </row>
     <row r="3">
@@ -530,34 +541,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Processador AMD Ryzen 5 7600</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>Processador</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Processador AMD Ryzen 5 7600</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Processador AMD Ryzen 5 7600, 3.8GHz (5.1GHz Max Turbo), Cache 38MB, 6 Núcleos, 12 Threads, AM5, Com Vídeo Integrado - 100-100001015BOX</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>999.99</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/405799/processador-amd-ryzen-5-7600-3-8ghz-5-1ghz-max-turbo-cache-38mb-6-nucleos-12-threads-am5-com-video-integrado-100-100001015box</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Processador AMD Ryzen 5 7600, 3.8GHz (5.1GHz Max Turbo), Cache 38MB, 6 Núcleos, 12 Threads, AM5, Com Vídeo Integrado - 100-100001015BOX</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>1823.52</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/405799/processador-amd-ryzen-5-7600-3-8ghz-5-1ghz-max-turbo-cache-38mb-6-nucleos-12-threads-am5-com-video-integrado-100-100001015box</t>
-        </is>
       </c>
     </row>
     <row r="4">
@@ -566,34 +582,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Processador AMD Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>Processador</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Processador AMD Ryzen 7 7800X3D</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Processador AMD Ryzen 7 7800x3d, 4.2GHz, 5.0GHz Max Turbo, Cache 104MB, Am5, C/ Vídeo E Sem Cooler - 100-100000910wof</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>1978.9</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/466557/processador-amd-ryzen-7-7800x3d-4-2ghz-5-0ghz-max-turbo-cache-104mb-am5-c-video-e-sem-cooler-100-100000910wof</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Processador AMD Ryzen 7 7800x3d, 4.2GHz, 5.0GHz Max Turbo, Cache 104MB, Am5, C/ Vídeo E Sem Cooler - 100-100000910wof</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>2264.19</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/466557/processador-amd-ryzen-7-7800x3d-4-2ghz-5-0ghz-max-turbo-cache-104mb-am5-c-video-e-sem-cooler-100-100000910wof</t>
-        </is>
       </c>
     </row>
     <row r="5">
@@ -602,34 +623,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Processador Intel Core i5-12400F</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>Processador</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Processador Intel Core i5-12400F</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Processador Intel Core i5-12400F, 2.5GHz (4.4GHz Max Turbo), Cache 18MB, 6 Núcleos, 12 Threads, LGA 1700, Sem Vídeo Integrado - BX8071512400F</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>859.99</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/283718/processador-intel-core-i5-12400f-2-5ghz-4-4ghz-max-turbo-cache-18mb-6-nucleos-12-threads-lga-1700-sem-video-integrado-bx8071512400f</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Processador Intel Core i5-12400F, 2.5GHz (4.4GHz Max Turbo), Cache 18MB, 6 Núcleos, 12 Threads, LGA 1700, Sem Vídeo Integrado - BX8071512400F</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>1658.32</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/283718/processador-intel-core-i5-12400f-2-5ghz-4-4ghz-max-turbo-cache-18mb-6-nucleos-12-threads-lga-1700-sem-video-integrado-bx8071512400f</t>
-        </is>
       </c>
     </row>
     <row r="6">
@@ -638,34 +664,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Processador Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>Processador</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Processador Intel Core i5-14400F</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Processador Intel Core I5 14400f 14ª Geração, 3.5 Ghz (4.7 Ghz Turbo), Cache 20mb, 10 Núcleos, 16 Threads, Lga1700, S/ Vídeo Integrado - Bx8071514400f</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>1069.99</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/531209/processador-intel-core-i5-14400f-14-geracao-3-5-ghz-4-7-ghz-turbo-cache-20mb-10-nucleos-16-threads-lga1700-sem-video-integrado-bx8071514400f</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Processador Intel Core I5 14400f 14ª Geração, 3.5 Ghz (4.7 Ghz Turbo), Cache 20mb, 10 Núcleos, 16 Threads, Lga1700, S/ Vídeo Integrado - Bx8071514400f</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>1189.99</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/531209/processador-intel-core-i5-14400f-14-geracao-3-5-ghz-4-7-ghz-turbo-cache-20mb-10-nucleos-16-threads-lga1700-sem-video-integrado-bx8071514400f</t>
-        </is>
       </c>
     </row>
     <row r="7">
@@ -674,34 +705,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Placa de Vídeo GeForce RTX 5060 8GB</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>Placa de Vídeo</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Placa de Vídeo GeForce RTX 5060 8GB</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Placa De Vídeo Inno3d Nvidia Geforce RTX 5060 Twin X2, 8GB, Gddr7, Dlss, Ray Tracing, N50602-08d7-195071n</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>2899.9</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/903752/gpu-inno3d-geforce-rtx-5060-twin-x2-8gb-128bits-gddr7-n50602-08d7-195071n</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Placa De Vídeo Inno3d Nvidia Geforce RTX 5060 Twin X2, 8GB, Gddr7, Dlss, Ray Tracing, N50602-08d7-195071n</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>3411.65</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/903752/gpu-inno3d-geforce-rtx-5060-twin-x2-8gb-128bits-gddr7-n50602-08d7-195071n</t>
-        </is>
       </c>
     </row>
     <row r="8">
@@ -710,34 +746,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Placa de Vídeo GeForce RTX 5070 12GB</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>Placa de Vídeo</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Placa de Vídeo GeForce RTX 5070 12GB</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Placa de Video Palit GeForce RTX 5070 WHITE OC 12GB GDDR7 192bit 3-DP e HDMI - NE75070U19K9-GB2050W</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>5299.99</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/989622/placa-de-video-palit-geforce-rtx-5070-white-oc-12gb-gddr7-192bit-3-dp-e-hdmi-ne75070u19k9-gb2050w</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Placa de Video Palit GeForce RTX 5070 WHITE OC 12GB GDDR7 192bit 3-DP e HDMI - NE75070U19K9-GB2050W</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>6666.66</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/989622/placa-de-video-palit-geforce-rtx-5070-white-oc-12gb-gddr7-192bit-3-dp-e-hdmi-ne75070u19k9-gb2050w</t>
-        </is>
       </c>
     </row>
     <row r="9">
@@ -746,34 +787,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Placa de Vídeo GeForce RTX 3060 12GB</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>Placa de Vídeo</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Placa de Vídeo GeForce RTX 3060 12GB</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Placa De Vídeo Husky Alpha RTX 3060, Nvidia, 12GB, GDDR6, 192-Bit, Dual Fan, HDMI, 3x DisplayPort - HVG023060</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>2199.99</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/996572/placa-de-video-husky-alpha-rtx-3060-nvidia-12gb-gddr6-192-bit-dual-fan-hdmi-3x-displayport-hvg023060</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Placa De Vídeo Husky Alpha RTX 3060, Nvidia, 12GB, GDDR6, 192-Bit, Dual Fan, HDMI, 3x DisplayPort - HVG023060</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>3529.4</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/996572/placa-de-video-husky-alpha-rtx-3060-nvidia-12gb-gddr6-192-bit-dual-fan-hdmi-3x-displayport-hvg023060</t>
-        </is>
       </c>
     </row>
     <row r="10">
@@ -782,34 +828,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Placa de Vídeo Radeon RX 7600 8GB</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>Placa de Vídeo</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Placa de Vídeo Radeon RX 7600 8GB</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Placa de Vídeo RX 7600 Challenger ASRock AMD Radeon,  8GB GDDR6 - 90-GA41ZZ-00UANF</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>1899.99</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/459144/placa-de-video-rx-7600-challenger-asrock-amd-radeon-8gb-gddr6-90-ga41zz-00uanf</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Placa de Vídeo RX 7600 Challenger ASRock AMD Radeon,  8GB GDDR6 - 90-GA41ZZ-00UANF</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>2823.52</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/459144/placa-de-video-rx-7600-challenger-asrock-amd-radeon-8gb-gddr6-90-ga41zz-00uanf</t>
-        </is>
       </c>
     </row>
     <row r="11">
@@ -818,34 +869,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Memória Kingston Fury Beast 8GB DDR4 3200MHz</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>Memória RAM</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Memória Kingston Fury Beast 8GB DDR4 3200MHz</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Memória Kingston Fury Beast 8GB, 3200MHz, DDR4, CL16, Preto - KF432C16BB/8</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>519.99</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/313833/memoria-kingston-fury-beast-8gb-3200mhz-ddr4-cl16-preto-kf432c16bb-8</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Memória Kingston Fury Beast 8GB, 3200MHz, DDR4, CL16, Preto - KF432C16BB/8</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>519.99</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/313833/memoria-kingston-fury-beast-8gb-3200mhz-ddr4-cl16-preto-kf432c16bb-8</t>
-        </is>
       </c>
     </row>
     <row r="12">
@@ -854,34 +910,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Memória Kingston Fury Beast 16GB DDR4 3200MHz</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>Memória RAM</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Memória Kingston Fury Beast 16GB DDR4 3200MHz</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Memória Ram Kingston Hyperx Fury Beast Ddr4 16gb 3200mhz Cl16 Udimm – Desktop</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>1016.41</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/938663/memoria-ram-kingston-hyperx-ddr4-16gb-2666mhz-cl16-udimm-desktop</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Memória Ram Kingston Hyperx Fury Beast Ddr4 16gb 3200mhz Cl16 Udimm – Desktop</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>1069.9</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/938663/memoria-ram-kingston-hyperx-ddr4-16gb-2666mhz-cl16-udimm-desktop</t>
-        </is>
       </c>
     </row>
     <row r="13">
@@ -890,34 +951,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Memória Kingston Fury Beast 16GB DDR5 5600MHz</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>Memória RAM</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Memória Kingston Fury Beast 16GB DDR5 5600MHz</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Memória RAM Kingston Fury Beast, 16GB, 5600MHz, DDR5, CL40, para Intel XMP, Preto - KF556C40BB-16</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>2049.99</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/285967/memoria-ram-kingston-fury-beast-16gb-5600mhz-ddr5-cl40-para-intel-xmp-preto-kf556c40bb-16</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Memória RAM Kingston Fury Beast, 16GB, 5600MHz, DDR5, CL40, para Intel XMP, Preto - KF556C40BB-16</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>2941.16</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/285967/memoria-ram-kingston-fury-beast-16gb-5600mhz-ddr5-cl40-para-intel-xmp-preto-kf556c40bb-16</t>
-        </is>
       </c>
     </row>
     <row r="14">
@@ -926,34 +992,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>SSD Kingston NV3 1TB M.2 NVMe</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>SSD</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>SSD Kingston NV3 1TB M.2 NVMe</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>SSD Kingston Nv3 1TB M.2 2280 Nvme Gen4, Desempenho E Eficiência Para Upgrade De PC – Snv3s/1000g</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>1139.05</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/1021928/ssd-kingston-nv3-1tb-m-2-2280-nvme-gen4-desempenho-e-eficiencia-para-upgrade-de-pc-snv3s-1000g</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>SSD Kingston Nv3 1TB M.2 2280 Nvme Gen4, Desempenho E Eficiência Para Upgrade De PC – Snv3s/1000g</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>1199</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/1021928/ssd-kingston-nv3-1tb-m-2-2280-nvme-gen4-desempenho-e-eficiencia-para-upgrade-de-pc-snv3s-1000g</t>
-        </is>
       </c>
     </row>
     <row r="15">
@@ -962,34 +1033,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>SSD Samsung 990 Pro 1TB M.2 NVMe</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>SSD</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>SSD Samsung 990 Pro 1TB M.2 NVMe</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>SSD Samsung 990 Pro 1TB, Nvme M.2 2280, Mz-v9p1t0b/am.</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>2399</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/464267/ssd-samsung-990-pro-1tb-nvme-m-2-2280-mz-v9p1t0b-am-</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>SSD Samsung 990 Pro 1TB, Nvme M.2 2280, Mz-v9p1t0b/am.</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
         <v>2399</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/464267/ssd-samsung-990-pro-1tb-nvme-m-2-2280-mz-v9p1t0b-am-</t>
-        </is>
       </c>
     </row>
     <row r="16">
@@ -998,34 +1074,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>SSD Kingston A400 480GB SATA</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>SSD</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>SSD Kingston A400 480GB SATA</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>SSD Kingston A400, 480GB, Sata Iii, 2.5", Leitura: 500mb/s, Gravação: 450mb/s, Preto - Sa400s37/480g</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>466.39</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/781777/ssd-kingston-a400-480gb-sata-iii-2-5-leitura-500mb-s-gravacao-450mb-s-preto-sa400s37-480g</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>SSD Kingston A400, 480GB, Sata Iii, 2.5", Leitura: 500mb/s, Gravação: 450mb/s, Preto - Sa400s37/480g</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
         <v>529.99</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/781777/ssd-kingston-a400-480gb-sata-iii-2-5-leitura-500mb-s-gravacao-450mb-s-preto-sa400s37-480g</t>
-        </is>
       </c>
     </row>
     <row r="17">
@@ -1034,34 +1115,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Placa-mãe ASUS TUF Gaming B550M-Plus</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>Placa-mãe</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Placa-mãe ASUS TUF Gaming B550M-Plus</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Placa-Mãe ASUS TUF Gaming B550M-Plus, AMD AM4, mATX, DDR4, Preto - 90MB14A0-C1BAY0</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>789.99</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/115216/placa-mae-asus-tuf-gaming-b550m-plus-amd-am4-matx-ddr4-preto-90mb14a0-c1bay0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Placa-Mãe ASUS TUF Gaming B550M-Plus, AMD AM4, mATX, DDR4, Preto - 90MB14A0-C1BAY0</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>1168</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/115216/placa-mae-asus-tuf-gaming-b550m-plus-amd-am4-matx-ddr4-preto-90mb14a0-c1bay0</t>
-        </is>
       </c>
     </row>
     <row r="18">
@@ -1070,34 +1156,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Placa-mãe MSI PRO B650M-P</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>Placa-mãe</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Placa-mãe MSI PRO B650M-P</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Placa Mãe MSI Pro B650M-P, AMD AM5, M-ATX, DDR5 - PRO B650M-P</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>896.99</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/524346/placa-mae-msi-pro-b650m-p-amd-am5-m-atx-ddr5-pro-b650m-p</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Placa Mãe MSI Pro B650M-P, AMD AM5, M-ATX, DDR5 - PRO B650M-P</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
         <v>1139.99</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/524346/placa-mae-msi-pro-b650m-p-amd-am5-m-atx-ddr5-pro-b650m-p</t>
-        </is>
       </c>
     </row>
     <row r="19">
@@ -1106,34 +1197,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Fonte Corsair CX650 650W 80 Plus Bronze</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>Fonte</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Fonte Corsair CX650 650W 80 Plus Bronze</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Fonte Corsair CX Series CX650, 650W, 80 Plus Bronze, Com Cabo, Preto - CP-9020278-BR</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>359.99</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/516056/fonte-corsair-cx-series-cx650-650w-80-plus-bronze-com-cabo-preto-cp-9020278-br</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Fonte Corsair CX Series CX650, 650W, 80 Plus Bronze, Com Cabo, Preto - CP-9020278-BR</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>433.32</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/516056/fonte-corsair-cx-series-cx650-650w-80-plus-bronze-com-cabo-preto-cp-9020278-br</t>
-        </is>
       </c>
     </row>
     <row r="20">
@@ -1142,34 +1238,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Fonte MSI MAG A650BN 650W 80 Plus Bronze</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>Fonte</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Fonte MSI MAG A650BN 650W 80 Plus Bronze</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Fonte MSI MAG A650BN, 650W, 80 Plus Bronze, PFC Ativo, Com Cabo, Preto - 306-7ZP2B22-CE0</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>349.99</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/369658/fonte-msi-mag-a650bn-650w-80-plus-bronze-pfc-ativo-com-cabo-preto-306-7zp2b22-ce0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Fonte MSI MAG A650BN, 650W, 80 Plus Bronze, PFC Ativo, Com Cabo, Preto - 306-7ZP2B22-CE0</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
         <v>388.88</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/369658/fonte-msi-mag-a650bn-650w-80-plus-bronze-pfc-ativo-com-cabo-preto-306-7zp2b22-ce0</t>
-        </is>
       </c>
     </row>
     <row r="21">
@@ -1178,38 +1279,43 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>kabum</t>
+          <t>KaBuM!</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>https://www.kabum.com.br</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Fonte XPG Core Reactor II VE 750W 80 Plus Gold</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>Fonte</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Fonte XPG Core Reactor II VE 750W 80 Plus Gold</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Fonte XPG Core Reactor II VE, 750W, 80 Plus Gold, Modular, PFC Ativo, Preto - 75261425</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>699.89</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/514895/fonte-xpg-core-reactor-ii-ve-750w-80-plus-gold-modular-pfc-ativo-preto-75261425</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Fonte XPG Core Reactor II VE, 750W, 80 Plus Gold, Modular, PFC Ativo, Preto - 75261425</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
         <v>777.66</v>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>https://www.kabum.com.br/produto/514895/fonte-xpg-core-reactor-ii-ve-750w-80-plus-gold-modular-pfc-ativo-preto-75261425</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H21"/>
+  <autoFilter ref="A1:I21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>